--- a/StructureDefinition-openimis-claim-administrator-practitioner-role.xlsx
+++ b/StructureDefinition-openimis-claim-administrator-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -10291,7 +10291,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>22</v>
@@ -10412,7 +10412,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>22</v>
@@ -10880,7 +10880,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>22</v>
@@ -10997,7 +10997,7 @@
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>22</v>
@@ -11112,7 +11112,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>22</v>
@@ -15312,7 +15312,7 @@
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-claim-administrator-practitioner-role.xlsx
+++ b/StructureDefinition-openimis-claim-administrator-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-claim-administrator-practitioner-role.xlsx
+++ b/StructureDefinition-openimis-claim-administrator-practitioner-role.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
